--- a/artfynd/A 31521-2025 artfynd.xlsx
+++ b/artfynd/A 31521-2025 artfynd.xlsx
@@ -776,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126514274</v>
+        <v>126514632</v>
       </c>
       <c r="B3" t="n">
         <v>78980</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467288</v>
+        <v>467433</v>
       </c>
       <c r="R3" t="n">
-        <v>6719006</v>
+        <v>6718618</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126514632</v>
+        <v>126514274</v>
       </c>
       <c r="B5" t="n">
         <v>78980</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467433</v>
+        <v>467288</v>
       </c>
       <c r="R5" t="n">
-        <v>6718618</v>
+        <v>6719006</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1489,7 +1489,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126514291</v>
+        <v>126514506</v>
       </c>
       <c r="B10" t="n">
         <v>78980</v>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467295</v>
+        <v>467301</v>
       </c>
       <c r="R10" t="n">
-        <v>6718987</v>
+        <v>6718683</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1590,7 +1590,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126514506</v>
+        <v>126514291</v>
       </c>
       <c r="B11" t="n">
         <v>78980</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467301</v>
+        <v>467295</v>
       </c>
       <c r="R11" t="n">
-        <v>6718683</v>
+        <v>6718987</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1792,46 +1792,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126514106</v>
+        <v>126514429</v>
       </c>
       <c r="B13" t="n">
-        <v>98382</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1839,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467360</v>
+        <v>467358</v>
       </c>
       <c r="R13" t="n">
-        <v>6718993</v>
+        <v>6718820</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1902,7 +1893,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126514429</v>
+        <v>126514285</v>
       </c>
       <c r="B14" t="n">
         <v>78980</v>
@@ -1940,10 +1931,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467358</v>
+        <v>467287</v>
       </c>
       <c r="R14" t="n">
-        <v>6718820</v>
+        <v>6718993</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2003,37 +1994,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126514285</v>
+        <v>126514234</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467287</v>
+        <v>467304</v>
       </c>
       <c r="R15" t="n">
-        <v>6718993</v>
+        <v>6718988</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2104,37 +2104,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126514234</v>
+        <v>126514106</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>98382</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467304</v>
+        <v>467360</v>
       </c>
       <c r="R16" t="n">
-        <v>6718988</v>
+        <v>6718993</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2214,46 +2214,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126514094</v>
+        <v>126514480</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2261,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467373</v>
+        <v>467266</v>
       </c>
       <c r="R17" t="n">
-        <v>6718996</v>
+        <v>6718781</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2324,43 +2315,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126514531</v>
+        <v>126514094</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>98361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2368,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467334</v>
+        <v>467373</v>
       </c>
       <c r="R18" t="n">
-        <v>6718718</v>
+        <v>6718996</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2431,37 +2425,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126514480</v>
+        <v>126514531</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467266</v>
+        <v>467334</v>
       </c>
       <c r="R19" t="n">
-        <v>6718781</v>
+        <v>6718718</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2734,46 +2734,43 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126514246</v>
+        <v>126514486</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>8447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2781,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467276</v>
+        <v>467290</v>
       </c>
       <c r="R22" t="n">
-        <v>6719005</v>
+        <v>6718725</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2844,43 +2841,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126514486</v>
+        <v>126514246</v>
       </c>
       <c r="B23" t="n">
-        <v>8447</v>
+        <v>98361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2888,10 +2888,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467290</v>
+        <v>467276</v>
       </c>
       <c r="R23" t="n">
-        <v>6718725</v>
+        <v>6719005</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126514511</v>
+        <v>126514455</v>
       </c>
       <c r="B28" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,21 +3367,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467316</v>
+        <v>467355</v>
       </c>
       <c r="R28" t="n">
-        <v>6718672</v>
+        <v>6718802</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3457,10 +3457,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126514455</v>
+        <v>126514511</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3468,21 +3468,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467355</v>
+        <v>467316</v>
       </c>
       <c r="R29" t="n">
-        <v>6718802</v>
+        <v>6718672</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3775,32 +3775,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126514611</v>
+        <v>126514588</v>
       </c>
       <c r="B32" t="n">
-        <v>92535</v>
+        <v>78738</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467384</v>
+        <v>467355</v>
       </c>
       <c r="R32" t="n">
-        <v>6718708</v>
+        <v>6718660</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3876,32 +3876,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126514588</v>
+        <v>126514611</v>
       </c>
       <c r="B33" t="n">
-        <v>78738</v>
+        <v>92535</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467355</v>
+        <v>467384</v>
       </c>
       <c r="R33" t="n">
-        <v>6718660</v>
+        <v>6718708</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -3977,46 +3977,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126514217</v>
+        <v>126514495</v>
       </c>
       <c r="B34" t="n">
-        <v>98361</v>
+        <v>78739</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4024,10 +4015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467336</v>
+        <v>467311</v>
       </c>
       <c r="R34" t="n">
-        <v>6718999</v>
+        <v>6718696</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4087,37 +4078,46 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126514495</v>
+        <v>126514217</v>
       </c>
       <c r="B35" t="n">
-        <v>78739</v>
+        <v>98361</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467311</v>
+        <v>467336</v>
       </c>
       <c r="R35" t="n">
-        <v>6718696</v>
+        <v>6718999</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>

--- a/artfynd/A 31521-2025 artfynd.xlsx
+++ b/artfynd/A 31521-2025 artfynd.xlsx
@@ -776,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126514632</v>
+        <v>126514274</v>
       </c>
       <c r="B3" t="n">
         <v>78980</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467433</v>
+        <v>467288</v>
       </c>
       <c r="R3" t="n">
-        <v>6718618</v>
+        <v>6719006</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126514367</v>
+        <v>126514632</v>
       </c>
       <c r="B4" t="n">
-        <v>92535</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467208</v>
+        <v>467433</v>
       </c>
       <c r="R4" t="n">
-        <v>6718837</v>
+        <v>6718618</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126514274</v>
+        <v>126514367</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>92535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467288</v>
+        <v>467208</v>
       </c>
       <c r="R5" t="n">
-        <v>6719006</v>
+        <v>6718837</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1792,37 +1792,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126514429</v>
+        <v>126514234</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1830,10 +1839,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467358</v>
+        <v>467304</v>
       </c>
       <c r="R13" t="n">
-        <v>6718820</v>
+        <v>6718988</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1893,37 +1902,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126514285</v>
+        <v>126514106</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>98382</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1931,7 +1949,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467287</v>
+        <v>467360</v>
       </c>
       <c r="R14" t="n">
         <v>6718993</v>
@@ -1994,46 +2012,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126514234</v>
+        <v>126514429</v>
       </c>
       <c r="B15" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2041,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467304</v>
+        <v>467358</v>
       </c>
       <c r="R15" t="n">
-        <v>6718988</v>
+        <v>6718820</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2104,46 +2113,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126514106</v>
+        <v>126514285</v>
       </c>
       <c r="B16" t="n">
-        <v>98382</v>
+        <v>78980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467360</v>
+        <v>467287</v>
       </c>
       <c r="R16" t="n">
         <v>6718993</v>

--- a/artfynd/A 31521-2025 artfynd.xlsx
+++ b/artfynd/A 31521-2025 artfynd.xlsx
@@ -776,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126514274</v>
+        <v>126514632</v>
       </c>
       <c r="B3" t="n">
         <v>78980</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467288</v>
+        <v>467433</v>
       </c>
       <c r="R3" t="n">
-        <v>6719006</v>
+        <v>6718618</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126514632</v>
+        <v>126514367</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>92535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467433</v>
+        <v>467208</v>
       </c>
       <c r="R4" t="n">
-        <v>6718618</v>
+        <v>6718837</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126514367</v>
+        <v>126514274</v>
       </c>
       <c r="B5" t="n">
-        <v>92535</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467208</v>
+        <v>467288</v>
       </c>
       <c r="R5" t="n">
-        <v>6718837</v>
+        <v>6719006</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1792,46 +1792,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126514234</v>
+        <v>126514429</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1839,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467304</v>
+        <v>467358</v>
       </c>
       <c r="R13" t="n">
-        <v>6718988</v>
+        <v>6718820</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1902,46 +1893,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126514106</v>
+        <v>126514285</v>
       </c>
       <c r="B14" t="n">
-        <v>98382</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1949,7 +1931,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467360</v>
+        <v>467287</v>
       </c>
       <c r="R14" t="n">
         <v>6718993</v>
@@ -2012,37 +1994,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126514429</v>
+        <v>126514234</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2050,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467358</v>
+        <v>467304</v>
       </c>
       <c r="R15" t="n">
-        <v>6718820</v>
+        <v>6718988</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2113,37 +2104,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126514285</v>
+        <v>126514106</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>98382</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467287</v>
+        <v>467360</v>
       </c>
       <c r="R16" t="n">
         <v>6718993</v>
